--- a/artfynd/A 26108-2022 artfynd.xlsx
+++ b/artfynd/A 26108-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -905,12 +905,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 26108-2022 artfynd.xlsx
+++ b/artfynd/A 26108-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107399</v>
       </c>
       <c r="B2" t="n">
-        <v>57678</v>
+        <v>57763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130107434</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26108-2022 artfynd.xlsx
+++ b/artfynd/A 26108-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130107399</v>
+        <v>130107434</v>
       </c>
       <c r="B2" t="n">
-        <v>57763</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100082</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,17 +708,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>förbiflygande</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Äskilt, Hl</t>
@@ -728,10 +722,10 @@
         <v>395505</v>
       </c>
       <c r="R2" t="n">
-        <v>6296273</v>
+        <v>6296172</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,24 +752,14 @@
           <t>2025-06-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-17</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Drog mot sydost</t>
+          <t>Flög iväg från några träd på hygget.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Örnborg</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -806,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107434</v>
+        <v>130107398</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,24 +823,30 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>förbiflygande</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NV om Äskilt, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395505</v>
+        <v>395591</v>
       </c>
       <c r="R3" t="n">
-        <v>6296172</v>
+        <v>6296208</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,14 +873,24 @@
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-17</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flög iväg från några träd på hygget.</t>
+          <t>Flög mot S</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,258 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Jonas Örnborg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Fågelinventering Bockåsen 2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130107399</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57890</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NV om Äskilt, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>395505</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6296273</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Drog mot sydost</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Andreas Ekedahl</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas Örnborg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fågelinventering Bockåsen 2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119154346</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bockåsen, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>395498</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6296330</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett par/en tuva.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Fågelinventering Bockåsen 2024-2025</t>
         </is>

--- a/artfynd/A 26108-2022 artfynd.xlsx
+++ b/artfynd/A 26108-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Fågelinventering Bockåsen 2024-2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107434</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
           <t>Fågelinventering Bockåsen 2024-2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107398</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1049,6 +1064,11 @@
           <t>Fågelinventering Bockåsen 2024-2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107399</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,8 +1186,19 @@
           <t>Fågelinventering Bockåsen 2024-2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119154346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>